--- a/artfynd/A 38923-2024 artfynd.xlsx
+++ b/artfynd/A 38923-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,6 +789,126 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>120159347</v>
+      </c>
+      <c r="B3" t="n">
+        <v>90957</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4217</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Evedal, Evedal, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>604662</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6515252</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På tallåga</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Göran Ekström, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38923-2024 artfynd.xlsx
+++ b/artfynd/A 38923-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>120159347</v>
       </c>
       <c r="B3" t="n">
-        <v>90957</v>
+        <v>90975</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 38923-2024 artfynd.xlsx
+++ b/artfynd/A 38923-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103679991</v>
+        <v>120159347</v>
       </c>
       <c r="B2" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>4217</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Larslundsmalmen, Srm</t>
+          <t>Evedal, Evedal, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604404.8586572601</v>
+        <v>604662</v>
       </c>
       <c r="R2" t="n">
-        <v>6515195.116102358</v>
+        <v>6515252</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -741,27 +738,32 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Lunda</t>
+          <t>Tuna</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På tallåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,72 +778,70 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Fredrik Enoksson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Enoksson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Lst D inventering sandbarrskogar</t>
-        </is>
-      </c>
+          <t>Göran Ekström, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120159347</v>
+        <v>101531503</v>
       </c>
       <c r="B3" t="n">
-        <v>90975</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4217</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Evedal, Evedal, Srm</t>
+          <t>Bergatuna, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604662</v>
+        <v>604393</v>
       </c>
       <c r="R3" t="n">
-        <v>6515252</v>
+        <v>6515232</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,32 +860,27 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Tuna</t>
+          <t>Lunda</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2022-06-09</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2022-06-09</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:58</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På tallåga</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,15 +895,223 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Ylva Linnman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Göran Ekström, Rolf Olsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Ylva Linnman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Lst D inventering sandbarrskogar</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>103679925</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Larslundsmalmen, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>604367</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6515219</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-09-21</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-09-21</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Fredrik Enoksson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Fredrik Enoksson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Lst D inventering sandbarrskogar</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>103679991</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Larslundsmalmen, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>604405</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6515195</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-09-21</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-09-21</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Fredrik Enoksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Fredrik Enoksson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Lst D inventering sandbarrskogar</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38923-2024 artfynd.xlsx
+++ b/artfynd/A 38923-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120159347</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -908,6 +918,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101531503</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1010,6 +1025,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103679925</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,8 +1132,19 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103679991</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>